--- a/.yuleosh/reports/layer2-report.xlsx
+++ b/.yuleosh/reports/layer2-report.xlsx
@@ -504,13 +504,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
     </row>
@@ -609,12 +609,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>passed</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>No prebuilt .elf found in tests/fixtures/prebuilt/. Compile with: cd tests/fixtures/hello-arm &amp;&amp; make</t>
+          <t>1 test(s) passed</t>
         </is>
       </c>
     </row>

--- a/.yuleosh/reports/layer2-report.xlsx
+++ b/.yuleosh/reports/layer2-report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stages" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Stages" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -500,17 +500,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>passed</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
     </row>
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -569,12 +569,19 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>passed</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>ARM ELF at /Users/stefan/.openclaw/workspace/yuleASR/build/yuleasr-cross-probe.elf</t>
+          <t>make returned 2: CMake Error at CMakeLists.txt:7 (project):
+  The CMAKE_C_COMPILER:
+    ARM_GCC_BIN_PATH-NOTFOUND/arm-none-eabi-gcc
+  is not a full path and was not found in the PATH.
+  Tell CMake where to find the compiler by setting either the environment
+  variable "CC" or the CMake cache entry CMAKE_C_COMPILER to the full path to
+  the compiler, or to the compiler name if it is in the PATH.
+CMake Error at</t>
         </is>
       </c>
     </row>
@@ -604,7 +611,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>sil-tests</t>
+          <t>misra-check</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -614,7 +621,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>1 test(s) passed</t>
+          <t>2211 MISRA violation(s) (4 required, 0 advisory) — see .yuleosh/reports/misra-report.json</t>
         </is>
       </c>
     </row>
@@ -626,15 +633,19 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>integration-tests</t>
+          <t>sil-tests</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>passed</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr"/>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>No prebuilt .elf found in tests/fixtures/prebuilt/. Compile with: cd tests/fixtures/hello-arm &amp;&amp; make</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -644,15 +655,33 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
+          <t>integration-tests</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
           <t>memory-safety</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>skipped</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>No ASan tests</t>
         </is>
